--- a/track2/AIREA_track2_methods_description_form.xlsx
+++ b/track2/AIREA_track2_methods_description_form.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD74B6C-924A-2047-8231-2C3F28DED6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27480" yWindow="15680" windowWidth="42340" windowHeight="26880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" xWindow="27480" yWindow="15680" windowWidth="42340" windowHeight="26880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Track 1 methods" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>Methods description — MVA Hackathon 2026, Track 1 (Variant Prediction)</t>
   </si>
@@ -170,6 +170,52 @@
   <si>
     <t>Please submit your answers with your Track 1 submission. All questions (with the exception of Question 1, in red) are voluntary; however, submissions without a methods description may be judged less favorably on the Innovation and Scalability criteria, since the panel can't assess what it can't see.
 Fill out this form once per model/approach submitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mechanism-first. (1) Read-level re-analysis of the participant's single-sample whole-genome data (locus-targeted realignment, robustness tests against control heterozygous sites, coding callability, structural screens, phase review) supports a known truncating BUB1B allele and finds a rare BUB1B missense change of unknown function; phase cannot be resolved; TRIP13, CEP57 and CENATAC cannot be ranked against each other. (2) Twelve curated approved-drug candidates were each assessed as a five-link causal chain (drug, target, cellular process, disease mechanism, phenotype), with FDA/EMA status verified, supporting and contradicting literature recorded, and a deterministic ranking rule applied. (3) Falsifiable in-vitro designs were specified for the surviving hypotheses and for the missense change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthropic, Claude Pro (consumer subscription), used through Claude Code with the model Claude Opus 5.5. Data-handling setting: model-training opt-out enabled ("Help improve Claude" off) and no feedback or ratings given on outputs (team-confirmed). Used for analysis scripting, public-API literature and regulatory retrieval, evidence tabulation, drafting and validation scripts. Command output, including variant-level information from the participant's data, was processed by this service. Whether any content was flagged for safety review is not visible to users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primarily manual curation with AI assistance. Candidates came from a curated review. Scripted Europe PMC, openFDA and EMA queries used generic drug, gene and process terms. No automated drug–target database screen generated candidates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract-level review (raw API text) of primary studies on: senolysis in BubR1 progeroid mice; NAD+/SIRT2 regulation of BubR1; aminoglycoside and ataluren read-through trials; antioxidant tumour promotion; microtubule-poison missegregation; BUBR1 pseudokinase function; MVA genetics. The ClinGen PS3/BS3 recommendations were read in full text. Each claim is traceable in an evidence ledger with its access level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public databases and literature only, plus the organiser-provided dataset under its terms. No proprietary data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">openFDA (drugsfda, label); EMA EPAR pages and medicines report; Europe PMC; GenCC; ClinVar (2026-10-04 release); gnomAD v4.1.1; UniProt 2026_03; AlphaFold DB v6; Ensembl 116 and MANE v1.5. OMIM was not used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss of function (dosage) for BUB1B. The truncating allele is predicted NMD-sensitive with an exact-allele ClinVar P/LP record; the missense change is functionally unclassified; phase is unresolved. The pathway is the spindle assembly checkpoint and kinetochore attachment (BUBR1, KARD/PP2A-B56); the downstream consequence is chromosome missegregation and mosaic aneuploidy. Reported as conditional, not established.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-assisted analysis sessions ran from 2026-10-19 to 2026-10-24. Human effort hours were not recorded and are not estimated here. Compute: one workstation; the largest step (a three-locus read screen) took about 4.6 hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We evaluated approved-drug hypotheses for mosaic variegated aneuploidy (MVA) using a participant's whole-genome data, with a mechanism-first approach.
+Variant analysis. We re-analysed the data at read level (locus-targeted realignment, robustness tests against control heterozygous sites from the same sample, coding callability, structural screens and a phase review). It supports a known truncating BUB1B allele, but it cannot classify a second, rare BUB1B missense change or resolve phase. A biallelic BUB1B mechanism is therefore conditional. Three other MVA genes (TRIP13, CEP57, CENATAC) showed no coding loss of function and could not be ranked against each other, and an intronic CEP57 structural signal remains unresolved.
+Drug assessment. Twelve previously curated candidates were each tested as a causal chain from drug to target, cellular process, disease mechanism and phenotype. FDA/EMA status was verified, supporting and contradicting literature was recorded, and a documented deterministic ranking rule was applied. No candidate has direct evidence of MVA-relevant benefit. Two approved drugs remain plausible but indirect research hypotheses:
+• dasatinib (senescent-cell clearance, a downstream effect);
+• niacin (NAD+/SIRT2-dependent BUBR1 abundance, relevant only if residual BUBR1 protein exists).
+Antioxidants, proteasome inhibition and spindle poisons are contradicted or potentially counterproductive. Read-through is weak, given the predicted nonsense-mediated decay.
+Experiments. We provide falsifiable in-vitro designs that separate rescue from growth inhibition, and a minimal functional programme for the missense change. Its interpretation is limited by the scarcity of classified pathogenic BUB1B missense controls.
+Strengths: explicit uncertainty; evidence labels on every claim; traceable sources with recorded access levels; a pre-declared ranking rule.
+Limitations:
+• literature mostly read at abstract level;
+• unresolved phase and missense function;
+• no wet-lab data;
+• validation scripts written by the same AI assistant as the analyses.
+The hypotheses are for follow-up and do not demonstrate efficacy.</t>
   </si>
 </sst>
 </file>
@@ -718,127 +764,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2" ht="16" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AIREA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2" ht="300" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mechanism-first. (1) Read-level re-analysis of the participant's single-sample whole-genome data (locus-targeted realignment, robustness tests against control heterozygous sites, coding callability, structural screens, phase review) supports a known truncating BUB1B allele and finds a rare BUB1B missense change of unknown function; phase cannot be resolved; TRIP13, CEP57 and CENATAC cannot be ranked against each other. (2) Twelve curated approved-drug candidates were each assessed as a five-link causal chain (drug, target, cellular process, disease mechanism, phenotype), with FDA/EMA status verified, supporting and contradicting literature recorded, and a deterministic ranking rule applied. (3) Falsifiable in-vitro designs were specified for the surviving hypotheses and for the missense change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2" ht="210" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anthropic, Claude Pro (consumer subscription), used through Claude Code with the model Claude Opus 5.5. Data-handling setting: model-training opt-out enabled ("Help improve Claude" off) and no feedback or ratings given on outputs (team-confirmed). Used for analysis scripting, public-API literature and regulatory retrieval, evidence tabulation, drafting and validation scripts. Command output, including variant-level information from the participant's data, was processed by this service. Whether any content was flagged for safety review is not visible to users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2" ht="90" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primarily manual curation with AI assistance. Candidates came from a curated review. Scripted Europe PMC, openFDA and EMA queries used generic drug, gene and process terms. No automated drug–target database screen generated candidates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2" ht="150" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abstract-level review (raw API text) of primary studies on: senolysis in BubR1 progeroid mice; NAD+/SIRT2 regulation of BubR1; aminoglycoside and ataluren read-through trials; antioxidant tumour promotion; microtubule-poison missegregation; BUBR1 pseudokinase function; MVA genetics. The ClinGen PS3/BS3 recommendations were read in full text. Each claim is traceable in an evidence ledger with its access level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2" ht="45" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Public databases and literature only, plus the organiser-provided dataset under its terms. No proprietary data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2" ht="75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">openFDA (drugsfda, label); EMA EPAR pages and medicines report; Europe PMC; GenCC; ClinVar (2026-10-04 release); gnomAD v4.1.1; UniProt 2026_03; AlphaFold DB v6; Ensembl 116 and MANE v1.5. OMIM was not used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2" ht="16" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2" ht="150" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loss of function (dosage) for BUB1B. The truncating allele is predicted NMD-sensitive with an exact-allele ClinVar P/LP record; the missense change is functionally unclassified; phase is unresolved. The pathway is the spindle assembly checkpoint and kinetochore attachment (BUBR1, KARD/PP2A-B56); the downstream consequence is chromosome missegregation and mosaic aneuploidy. Reported as conditional, not established.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2" ht="90" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI-assisted analysis sessions ran from 2026-10-19 to 2026-10-24. Human effort hours were not recorded and are not estimated here. Compute: one workstation; the largest step (a three-locus read screen) took about 4.6 hours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2" ht="409" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We evaluated approved-drug hypotheses for mosaic variegated aneuploidy (MVA) using a participant's whole-genome data, with a mechanism-first approach.
-Variant analysis. We re-analysed the data at read level (locus-targeted realignment, robustness tests against control heterozygous sites from the same sample, coding callability, structural screens and a phase review). It supports a known truncating BUB1B allele, but it cannot classify a second, rare BUB1B missense change or resolve phase. A biallelic BUB1B mechanism is therefore conditional. Three other MVA genes (TRIP13, CEP57, CENATAC) showed no coding loss of function and could not be ranked against each other, and an intronic CEP57 structural signal remains unresolved.
-Drug assessment. Twelve previously curated candidates were each tested as a causal chain from drug to target, cellular process, disease mechanism and phenotype. FDA/EMA status was verified, supporting and contradicting literature was recorded, and a documented deterministic ranking rule was applied. No candidate has direct evidence of MVA-relevant benefit. Two approved drugs remain plausible but indirect research hypotheses:
-• dasatinib (senescent-cell clearance, a downstream effect);
-• niacin (NAD+/SIRT2-dependent BUBR1 abundance, relevant only if residual BUBR1 protein exists).
-Antioxidants, proteasome inhibition and spindle poisons are contradicted or potentially counterproductive. Read-through is weak, given the predicted nonsense-mediated decay.
-Experiments. We provide falsifiable in-vitro designs that separate rescue from growth inhibition, and a minimal functional programme for the missense change. Its interpretation is limited by the scarcity of classified pathogenic BUB1B missense controls.
-Strengths: explicit uncertainty; evidence labels on every claim; traceable sources with recorded access levels; a pre-declared ranking rule.
-Limitations:
-• literature mostly read at abstract level;
-• unresolved phase and missense function;
-• no wet-lab data;
-• validation scripts written by the same AI assistant as the analyses.
-The hypotheses are for follow-up and do not demonstrate efficacy.</t>
-        </is>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
